--- a/docs/files/exports/docs-website-website-pricing-parameters.xlsx
+++ b/docs/files/exports/docs-website-website-pricing-parameters.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1,785 words</t>
+          <t>1,885 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>🌐 Website Pricing Parameters — Quick Reference Sheet Purpose: A condensed pricing reference to quickly calculate project costs. Use after the Client Questionnaire to map requirements to prices. How to Use This Sheet Go t...</t>
+          <t>🌐 Website Pricing Parameters — Quick Reference Sheet Purpose: A condensed pricing reference to quickly calculate project costs. Use after the Client Questionnaire to map requirements to prices. How to Use This Sheet + Ad...</t>
         </is>
       </c>
     </row>
